--- a/datos/diccionarios/Diccionario de DIVIPOLA.xlsx
+++ b/datos/diccionarios/Diccionario de DIVIPOLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://konradlorenzedu-my.sharepoint.com/personal/angien_sanchezm_konradlorenz_edu_co/Documents/Proyecto Inteligencia de Negocios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBD0E4BC-8C3D-4481-A5B1-B68F8C038823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{DBD0E4BC-8C3D-4481-A5B1-B68F8C038823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42771A09-1F85-46D8-9496-E559E424A217}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A961851C-3C92-42D0-BC2C-543402ECC083}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>Campo</t>
   </si>
@@ -73,18 +73,6 @@
   </si>
   <si>
     <t>Los 1.122 códigos revisados no tienen vacíos y son únicos; usar este campo para relacionar registros.</t>
-  </si>
-  <si>
-    <t>Nombre Municipio</t>
-  </si>
-  <si>
-    <t>Nombre oficial del municipio o área correspondiente.</t>
-  </si>
-  <si>
-    <t>MEDELLÍN</t>
-  </si>
-  <si>
-    <t>El nombre no es una clave única: ALBÁN aparece en Cundinamarca y Nariño. Relacionar usando Código Municipio.</t>
   </si>
   <si>
     <t>Tipo: Municipio / Isla / Área no municipalizada</t>
@@ -517,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A449E8-DA55-4CF1-A247-B8A8A2BA76DE}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
@@ -596,71 +584,54 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3">
+        <v>-75.581774999999993</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3">
-        <v>-75.581774999999993</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="D7" s="2">
         <v>6.2466309999999998</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
+      <c r="E7" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
